--- a/STUDIO/org.openl.rules.demo/src/org.openl.rules.demo.tutorials/Tutorial 8 - Introduction to Smart Rules and Smart Lookup Tables/rules/Tutorial8 - Introduction to Smart Rules and Smart Lookup Tables.xlsx
+++ b/STUDIO/org.openl.rules.demo/src/org.openl.rules.demo.tutorials/Tutorial 8 - Introduction to Smart Rules and Smart Lookup Tables/rules/Tutorial8 - Introduction to Smart Rules and Smart Lookup Tables.xlsx
@@ -179,7 +179,7 @@
     <t>Excluded, Non-Driver</t>
   </si>
   <si>
-    <t>= $600 * ( 1 + 15%)</t>
+    <t>= 600 * ( 1 + 15%)</t>
   </si>
   <si>
     <r>
@@ -1091,16 +1091,16 @@
     </r>
   </si>
   <si>
-    <t>= min ( $550, $600 * (1 - discount ) )</t>
-  </si>
-  <si>
-    <t>= min ( $700, $750 * (1 - discount ) )</t>
-  </si>
-  <si>
-    <t>= min ( $550, $600 * ( 1 - discount ) )</t>
-  </si>
-  <si>
-    <t>= min ( $700, $750 * ( 1 - discount ) )</t>
+    <t>= min ( 550, 600 * (1 - discount ) )</t>
+  </si>
+  <si>
+    <t>= min ( 700, 750 * (1 - discount ) )</t>
+  </si>
+  <si>
+    <t>= min ( 550, 600 * ( 1 - discount ) )</t>
+  </si>
+  <si>
+    <t>= min ( 700, 750 * ( 1 - discount ) )</t>
   </si>
   <si>
     <t>Tutorial8 - Smart Rules and Smart Lookup Tables</t>
